--- a/SCH-STH/Impact assessments/Senegal/2025/octobre/sn_sppa_impact_2510_1_site.xlsx
+++ b/SCH-STH/Impact assessments/Senegal/2025/octobre/sn_sppa_impact_2510_1_site.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\yumbad\Repositories\dsa-forms\SCH-STH\Impact assessments\Senegal\2025\octobre\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7E3625D-92E0-47B1-BF87-7EA590CE3B23}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{79A0723B-E9E5-4A64-B3D7-FEEB1BDA9D46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="498" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" tabRatio="498" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="survey" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2260" uniqueCount="523">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2273" uniqueCount="524">
   <si>
     <t>type</t>
   </si>
@@ -1749,10 +1749,13 @@
     </r>
   </si>
   <si>
-    <t>(2025 Oct) - 1. SCH/STH – Site</t>
-  </si>
-  <si>
-    <t>sn_sppa_impact_2510_1_site</t>
+    <t>sn_sppa_impact_2510_1_site_v2</t>
+  </si>
+  <si>
+    <t>(2025 Oct) - 1. SCH/STH – Site V2</t>
+  </si>
+  <si>
+    <t>select_one yesNoDontKnow</t>
   </si>
 </sst>
 </file>
@@ -2876,7 +2879,9 @@
       <c r="G15" s="18"/>
       <c r="H15" s="17"/>
       <c r="I15" s="17"/>
-      <c r="J15" s="17"/>
+      <c r="J15" s="17" t="s">
+        <v>13</v>
+      </c>
       <c r="K15" s="17"/>
       <c r="L15" s="15"/>
       <c r="M15" s="17"/>
@@ -3099,7 +3104,9 @@
         <v>173</v>
       </c>
       <c r="I24" s="17"/>
-      <c r="J24" s="17"/>
+      <c r="J24" s="17" t="s">
+        <v>13</v>
+      </c>
       <c r="K24" s="17"/>
       <c r="L24" s="17"/>
       <c r="M24" s="17"/>
@@ -3122,7 +3129,9 @@
         <v>188</v>
       </c>
       <c r="I25" s="17"/>
-      <c r="J25" s="17"/>
+      <c r="J25" s="17" t="s">
+        <v>13</v>
+      </c>
       <c r="K25" s="17"/>
       <c r="L25" s="17"/>
       <c r="M25" s="17"/>
@@ -3145,7 +3154,9 @@
         <v>188</v>
       </c>
       <c r="I26" s="17"/>
-      <c r="J26" s="17"/>
+      <c r="J26" s="17" t="s">
+        <v>13</v>
+      </c>
       <c r="K26" s="17"/>
       <c r="L26" s="17"/>
       <c r="M26" s="17"/>
@@ -3168,7 +3179,9 @@
         <v>188</v>
       </c>
       <c r="I27" s="17"/>
-      <c r="J27" s="17"/>
+      <c r="J27" s="17" t="s">
+        <v>13</v>
+      </c>
       <c r="K27" s="17"/>
       <c r="L27" s="17"/>
       <c r="M27" s="17"/>
@@ -3191,7 +3204,9 @@
         <v>177</v>
       </c>
       <c r="I28" s="17"/>
-      <c r="J28" s="17"/>
+      <c r="J28" s="17" t="s">
+        <v>13</v>
+      </c>
       <c r="K28" s="17"/>
       <c r="L28" s="17"/>
       <c r="M28" s="17"/>
@@ -3214,7 +3229,9 @@
         <v>177</v>
       </c>
       <c r="I29" s="17"/>
-      <c r="J29" s="17"/>
+      <c r="J29" s="17" t="s">
+        <v>13</v>
+      </c>
       <c r="K29" s="17"/>
       <c r="L29" s="17"/>
       <c r="M29" s="17"/>
@@ -3237,7 +3254,9 @@
         <v>178</v>
       </c>
       <c r="I30" s="17"/>
-      <c r="J30" s="17"/>
+      <c r="J30" s="17" t="s">
+        <v>13</v>
+      </c>
       <c r="K30" s="17"/>
       <c r="L30" s="17"/>
       <c r="M30" s="17"/>
@@ -3260,7 +3279,9 @@
         <v>176</v>
       </c>
       <c r="I31" s="22"/>
-      <c r="J31" s="17"/>
+      <c r="J31" s="17" t="s">
+        <v>13</v>
+      </c>
       <c r="K31" s="22"/>
       <c r="L31" s="22"/>
       <c r="M31" s="22"/>
@@ -3283,7 +3304,9 @@
         <v>179</v>
       </c>
       <c r="I32" s="22"/>
-      <c r="J32" s="17"/>
+      <c r="J32" s="17" t="s">
+        <v>13</v>
+      </c>
       <c r="K32" s="22"/>
       <c r="L32" s="22"/>
       <c r="M32" s="22"/>
@@ -3306,7 +3329,9 @@
         <v>180</v>
       </c>
       <c r="I33" s="22"/>
-      <c r="J33" s="17"/>
+      <c r="J33" s="17" t="s">
+        <v>13</v>
+      </c>
       <c r="K33" s="22"/>
       <c r="L33" s="22"/>
       <c r="M33" s="22"/>
@@ -3329,7 +3354,9 @@
         <v>181</v>
       </c>
       <c r="I34" s="22"/>
-      <c r="J34" s="17"/>
+      <c r="J34" s="17" t="s">
+        <v>13</v>
+      </c>
       <c r="K34" s="22"/>
       <c r="L34" s="22"/>
       <c r="M34" s="22"/>
@@ -3360,8 +3387,8 @@
       <c r="M35" s="22"/>
     </row>
     <row r="36" spans="1:13" ht="63" x14ac:dyDescent="0.25">
-      <c r="A36" s="17" t="s">
-        <v>23</v>
+      <c r="A36" s="20" t="s">
+        <v>523</v>
       </c>
       <c r="B36" s="25" t="s">
         <v>183</v>
@@ -3377,7 +3404,9 @@
         <v>174</v>
       </c>
       <c r="I36" s="17"/>
-      <c r="J36" s="17"/>
+      <c r="J36" s="17" t="s">
+        <v>13</v>
+      </c>
       <c r="K36" s="17"/>
       <c r="L36" s="17"/>
       <c r="M36" s="17"/>
@@ -12639,10 +12668,10 @@
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
+        <v>522</v>
+      </c>
+      <c r="B2" s="11" t="s">
         <v>521</v>
-      </c>
-      <c r="B2" s="11" t="s">
-        <v>522</v>
       </c>
       <c r="C2" t="s">
         <v>69</v>
